--- a/docs/downloads/04/tbl_cm_educ_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_alaotra_ambodivoara.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -438,32 +438,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>13.8</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>1.7</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +474,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C7">
-        <v>51</v>
+        <v>307</v>
       </c>
       <c r="D7">
-        <v>10.1</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="8">
@@ -492,14 +492,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C8">
-        <v>307</v>
+        <v>109</v>
       </c>
       <c r="D8">
-        <v>60.6</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="9">
@@ -510,50 +510,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C9">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="D9">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>34</v>
-      </c>
-      <c r="D10">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>1.2</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_educ_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_cm_educ_alaotra_ambodivoara.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,12 +387,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>8.6</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -402,14 +396,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>31</v>
-      </c>
-      <c r="D3">
-        <v>53.4</v>
+          <t>Non scolarisé</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -420,14 +408,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>22.4</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="5">
@@ -438,32 +426,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>15.5</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C6">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>10.1</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +462,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C7">
-        <v>307</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>60.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -492,14 +480,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C8">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>21.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="9">
@@ -510,13 +498,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>307</v>
+      </c>
+      <c r="D9">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>109</v>
+      </c>
+      <c r="D10">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="C9">
+      <c r="C11">
         <v>40</v>
       </c>
-      <c r="D9">
+      <c r="D11">
         <v>7.9</v>
       </c>
     </row>
